--- a/Corpus_of_tests/Delta/requirements.xlsx
+++ b/Corpus_of_tests/Delta/requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\TFM_Generation-of-ontology-tests-using-Large-Language-Models\Corpus_of_tests\Delta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{602EF12C-96E9-4D8F-9ABF-C869C84E6438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5980F34C-4DE6-4534-83A5-9DC2EA4959A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9420" xr2:uid="{0A01FEE9-5AFC-4377-9E75-9E7227D8A404}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{0A01FEE9-5AFC-4377-9E75-9E7227D8A404}"/>
   </bookViews>
   <sheets>
     <sheet name="requirements" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="59">
   <si>
     <t>Identifier (domain+id)</t>
   </si>
@@ -38,12 +38,6 @@
 Natural language sentence (fact)</t>
   </si>
   <si>
-    <t>Answer</t>
-  </si>
-  <si>
-    <t>Status (Proposed, Accepted, Rejected, Pending, Deprecated)</t>
-  </si>
-  <si>
     <t>delta-2</t>
   </si>
   <si>
@@ -54,9 +48,6 @@
   </si>
   <si>
     <t>There is a power provider and recipient</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
   <si>
     <t>delta-25</t>
@@ -214,7 +205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,8 +340,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,8 +538,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -646,6 +660,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -691,10 +720,25 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1071,10 +1115,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA76691-DBE5-40C5-9FFE-83AB2E603F36}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="41.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1090,434 +1137,366 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
+    </row>
+    <row r="5" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5">
+      <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="E7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6">
+    </row>
+    <row r="8" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="80.400000000000006" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="80.400000000000006" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="6">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9">
+    </row>
+    <row r="11" spans="1:5" ht="80.400000000000006" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="6">
         <v>2</v>
       </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="E11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10">
+    </row>
+    <row r="12" spans="1:5" ht="80.400000000000006" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="6">
         <v>2</v>
       </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="67.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D13" s="6">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D13">
+      <c r="D14" s="6">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="6">
+        <v>5</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="6">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="6">
+        <v>5</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="6">
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="6">
+        <v>5</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="6">
         <v>3</v>
       </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16">
-        <v>5</v>
-      </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="E20" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19">
-        <v>5</v>
-      </c>
-      <c r="E19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D21" s="6">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D20">
+    </row>
+    <row r="22" spans="1:5" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="6">
         <v>3</v>
       </c>
-      <c r="E20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="E22" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>